--- a/웨딩홀 정보.xlsx
+++ b/웨딩홀 정보.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10308"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimdohyeon/Desktop/결혼식/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5B7D4D75-3650-3B4A-9802-A08BB91168D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4D7C9E-FF21-7C48-AD32-14292F1B4D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -219,7 +219,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="900" uniqueCount="381">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="387">
   <si>
     <t>서울 웨딩홀 마스터북 v2 (지도 보이게 / 플래너형)</t>
   </si>
@@ -1386,6 +1386,30 @@
   </si>
   <si>
     <t>성균관컨벤션웨딩홀</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>아이벡스 컨벤션</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>광명시</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기 광명시 양지로 17</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>경기도</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.ivexwed.co.kr/</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://map.naver.com/p/entry/place/2088999432?c=15.00,0,0,0,dh&amp;placePath=/home?from=map&amp;fromPanelNum=1&amp;additionalHeight=76&amp;timestamp=202605312335&amp;locale=ko&amp;svcName=map_pcv5</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2907,7 +2931,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:AV46"/>
+  <dimension ref="A1:AV47"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="17"/>
   <cols>
     <col min="1" max="1" width="5" style="13" customWidth="1"/>
@@ -9598,10 +9622,132 @@
       </c>
       <c r="AV46" s="23"/>
     </row>
+    <row r="47" spans="1:48">
+      <c r="A47" s="14">
+        <v>61</v>
+      </c>
+      <c r="B47" s="14" t="s">
+        <v>381</v>
+      </c>
+      <c r="C47" s="14" t="s">
+        <v>382</v>
+      </c>
+      <c r="D47" s="14" t="s">
+        <v>383</v>
+      </c>
+      <c r="E47" s="14" t="s">
+        <v>384</v>
+      </c>
+      <c r="F47" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="G47" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="H47" s="14" t="s">
+        <v>364</v>
+      </c>
+      <c r="I47" s="14">
+        <v>80</v>
+      </c>
+      <c r="J47" s="14">
+        <v>1</v>
+      </c>
+      <c r="K47" s="14" t="s">
+        <v>365</v>
+      </c>
+      <c r="L47" s="16">
+        <v>90000</v>
+      </c>
+      <c r="M47" s="16">
+        <v>95000</v>
+      </c>
+      <c r="N47" s="17">
+        <v>95000</v>
+      </c>
+      <c r="O47" s="16">
+        <v>240</v>
+      </c>
+      <c r="P47" s="16">
+        <v>500</v>
+      </c>
+      <c r="Q47" s="16">
+        <v>10500000</v>
+      </c>
+      <c r="R47" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="S47" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="T47" s="16" t="s">
+        <v>357</v>
+      </c>
+      <c r="U47" s="16"/>
+      <c r="V47" s="18" t="str">
+        <f t="shared" ref="V47" si="33">IF(AND(T47="",AB47&gt;0),ROUND(AB47*10%,-4),T47)</f>
+        <v>-</v>
+      </c>
+      <c r="W47" s="26" t="s">
+        <v>385</v>
+      </c>
+      <c r="X47" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="Y47" s="26" t="s">
+        <v>386</v>
+      </c>
+      <c r="Z47" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="AA47" s="17"/>
+      <c r="AB47" s="17"/>
+      <c r="AC47" s="20" t="e">
+        <f t="shared" ref="AC47" si="34">IF(AND(L47&gt;0,N47&gt;0),L47*N47+IF(P47="",0,P47)+IF(Q47="",0,Q47)+IF(S47="",0,S47),"")</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AD47" s="21"/>
+      <c r="AE47" s="19"/>
+      <c r="AF47" s="17"/>
+      <c r="AG47" s="22"/>
+      <c r="AH47" s="22"/>
+      <c r="AI47" s="14"/>
+      <c r="AJ47" s="13" t="str">
+        <f t="shared" ref="AJ47" si="35">IF(OR(C47="강남구",C47="서초구",C47="송파구"),"강남권","비강남권")</f>
+        <v>비강남권</v>
+      </c>
+      <c r="AK47" s="13" t="str">
+        <f t="shared" ref="AK47" si="36">IF(C47="강남구","강남",IF(C47="서초구","서초",IF(C47="송파구","송파",IF(C47="영등포구","영등포",IF(C47="마포구","마포","기타")))))</f>
+        <v>기타</v>
+      </c>
+      <c r="AL47" s="23"/>
+      <c r="AM47" s="24" t="e">
+        <f t="shared" ref="AM47" si="37">IF(B47="","",MIN(5,IF(ISNUMBER(SEARCH("역",AC47)),4,IF(AC47&lt;&gt;"",3,2))+IF(Z47&lt;&gt;"",1,0)))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AN47" s="24"/>
+      <c r="AO47" s="24"/>
+      <c r="AP47" s="24"/>
+      <c r="AQ47" s="23"/>
+      <c r="AR47" s="23"/>
+      <c r="AS47" s="24" t="e">
+        <f>IF(B47="","",ROUND(AN47*Assumptions!$B$3+AO47*Assumptions!$B$4+AM47*Assumptions!$B$5+AP47*Assumptions!$B$6+AQ47*Assumptions!$B$7+AR47*Assumptions!$B$8,2))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AT47" s="25" t="e">
+        <f t="shared" ref="AT47" si="38">IF(AS47="","",IF(AS47&gt;=4.2,"A",IF(AS47&gt;=3.4,"B","C")))</f>
+        <v>#VALUE!</v>
+      </c>
+      <c r="AU47" s="25" t="str">
+        <f t="shared" ref="AU47" si="39">IF(AD47="","",IF(AD47&lt;=25000000,"~2.5억",IF(AD47&lt;=35000000,"2.5~3.5억",IF(AD47&lt;=50000000,"3.5~5억","5억+"))))</f>
+        <v/>
+      </c>
+      <c r="AV47" s="23"/>
+    </row>
   </sheetData>
   <autoFilter ref="A1:AH46" xr:uid="{00000000-0009-0000-0000-000002000000}"/>
   <phoneticPr fontId="8" type="noConversion"/>
-  <conditionalFormatting sqref="AS2:AS46">
+  <conditionalFormatting sqref="AS2:AS47">
     <cfRule type="colorScale" priority="17">
       <colorScale>
         <cfvo type="min"/>
@@ -9613,16 +9759,19 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" sqref="G2:G46" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations disablePrompts="1" count="1">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G47" xr:uid="{00000000-0002-0000-0200-000000000000}">
       <formula1>"밝은홀,어두운홀,혼합"</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
     <hyperlink ref="W26" r:id="rId1" xr:uid="{21FFE36A-8236-A841-AE6B-6E427A4848F8}"/>
+    <hyperlink ref="W47" r:id="rId2" xr:uid="{28C2D475-3E5D-A749-AF2F-B0975FB6D7E9}"/>
+    <hyperlink ref="Y47" r:id="rId3" xr:uid="{DCFB40F5-CF7E-A842-9F53-C65AFBD607AC}"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <legacyDrawing r:id="rId4"/>
 </worksheet>
 </file>
 

--- a/웨딩홀 정보.xlsx
+++ b/웨딩홀 정보.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kimdohyeon/Desktop/결혼식/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FA4D7C9E-FF21-7C48-AD32-14292F1B4D8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19EC1AD7-D1EF-EB4F-AF3B-E143A1BFD6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="16060" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -219,7 +219,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="915" uniqueCount="387">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="914" uniqueCount="387">
   <si>
     <t>서울 웨딩홀 마스터북 v2 (지도 보이게 / 플래너형)</t>
   </si>
@@ -9657,7 +9657,7 @@
         <v>365</v>
       </c>
       <c r="L47" s="16">
-        <v>90000</v>
+        <v>120000</v>
       </c>
       <c r="M47" s="16">
         <v>95000</v>
@@ -9666,16 +9666,16 @@
         <v>95000</v>
       </c>
       <c r="O47" s="16">
-        <v>240</v>
+        <v>300</v>
       </c>
       <c r="P47" s="16">
-        <v>500</v>
+        <v>800</v>
       </c>
       <c r="Q47" s="16">
+        <v>16500000</v>
+      </c>
+      <c r="R47" s="16">
         <v>10500000</v>
-      </c>
-      <c r="R47" s="16" t="s">
-        <v>357</v>
       </c>
       <c r="S47" s="16" t="s">
         <v>357</v>
